--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1998,7 +1998,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
@@ -562,7 +562,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1119,11 @@
           <t>77.549.439-5</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1184,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1249,11 @@
           <t>77.314.274-2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2290,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2477,11 @@
           <t>77.864.159-3</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2725,11 @@
           <t>77.549.439-5</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2790,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3160,11 @@
           <t>77.659.446-6</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3225,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3290,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3416,11 @@
           <t>77.551.961-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3481,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4095,11 @@
           <t>77.314.274-2</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4221,11 @@
           <t>77.173.533-9</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4286,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4351,11 @@
           <t>11.844.234-2</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4538,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4603,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5095,11 @@
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
@@ -4668,7 +4668,11 @@
           <t>78.973.230-2</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -3227,7 +3227,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3292,7 +3292,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4605,7 +4605,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">

--- a/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
+++ b/docs/oc-mensuales/transporte-privado-de-pasajeros-y-arriendo-de-vehiculos/ago-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -782,7 +782,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2677,7 +2677,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4451-503-CM26</t>
+          <t>934-134-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2702,32 +2702,32 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>TRANSPORTES TOGUITA SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>77.549.439-5</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2736,13 +2736,13 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>6504.94</v>
+        <v>3942.4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>934-134-CM26</t>
+          <t>4451-503-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2767,32 +2767,32 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>PAULA ANDREA MERY NAVIA</t>
+          <t>TRANSPORTES TOGUITA SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>11.844.234-2</t>
+          <t>77.549.439-5</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3942.4</v>
+        <v>6504.94</v>
       </c>
     </row>
     <row r="39">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3112,7 +3112,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>934-136-CM26</t>
+          <t>934-137-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
+          <t>PAULA ANDREA MERY NAVIA</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.659.446-6</t>
+          <t>11.844.234-2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3171,13 +3171,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>878.41</v>
+        <v>5292.15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1495208-17-CM26</t>
+          <t>934-136-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3197,37 +3197,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TURISMO Y EXCURSIONES PATAGON AUSTRAL SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.659.446-6</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3236,7 +3236,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>11707.46</v>
+        <v>878.41</v>
       </c>
     </row>
     <row r="46">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1134432-587-CM26</t>
+          <t>1495208-17-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3327,48 +3327,52 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3730.53</v>
+        <v>11707.46</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1080089-504-CM26</t>
+          <t>1134432-587-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3393,47 +3397,43 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.607.900-k</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD MAGALLANES</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TRANSPORTES, RENT A CAR Y LOGÍSTICA RAMÓN VILLABLANCA BARRIENTOS E.I.R</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>77.551.961-4</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Valparaíso</t>
-        </is>
-      </c>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>8458.77</v>
+        <v>3730.53</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1385462-131-CM26</t>
+          <t>1080089-504-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3458,32 +3458,32 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>TRANSPORTES, RENT A CAR Y LOGÍSTICA RAMÓN VILLABLANCA BARRIENTOS E.I.R</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.551.961-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3492,13 +3492,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>11707.46</v>
+        <v>8458.77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2408-777-CM26</t>
+          <t>1385462-131-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3513,53 +3513,57 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.170.100-K</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>76.791.832-1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10663.29</v>
+        <v>11707.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057499-434-CM26</t>
+          <t>2408-777-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3574,7 +3578,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3584,27 +3588,27 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>69.170.100-K</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t xml:space="preserve">esteban jesus </t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.252.815-0</t>
+          <t>76.470.279-4</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3614,13 +3618,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>62389.65</v>
+        <v>10663.29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>1134432-597-CM26</t>
+          <t>1057499-434-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3645,27 +3649,27 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>69.060.800-6</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t xml:space="preserve">esteban jesus </t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.252.815-0</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3675,13 +3679,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>303.28</v>
+        <v>62389.65</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1260-124-CM26</t>
+          <t>1134432-597-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3696,37 +3700,37 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.923.200-3</t>
+          <t>69.060.800-6</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
+          <t>I MUNICIPALIDAD DE PUCHUNCAVI</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.902.907-9</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
@@ -3736,7 +3740,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>26138.95</v>
+        <v>303.28</v>
       </c>
     </row>
     <row r="54">
@@ -3803,7 +3807,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1078634-13-CM26</t>
+          <t>1260-124-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3818,37 +3822,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.402.010-5</t>
+          <t>61.923.200-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MINISTERIO DE BIENES NACIONALES</t>
+          <t>GOBIERNO REGIONAL REGION METROPOLITANA</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>David Isaac</t>
+          <t>TRANSPORTES LUCIANO ESPINOZA E.I.R.L.</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.820.816-6</t>
+          <t>76.902.907-9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3858,7 +3862,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>43733.05</v>
+        <v>26138.95</v>
       </c>
     </row>
     <row r="56">
@@ -3925,7 +3929,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1198-203-CM26</t>
+          <t>1078634-13-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3950,27 +3954,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.402.010-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>MINISTERIO DE BIENES NACIONALES</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>David Isaac</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.820.816-6</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3980,13 +3984,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>5193.3</v>
+        <v>43733.05</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057417-15339-CM26</t>
+          <t>1198-203-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4001,7 +4005,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -4011,27 +4015,27 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>TURISMO AYEKANTUN LIMITADA</t>
+          <t xml:space="preserve">Felipe </t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.470.279-4</t>
+          <t>76.834.013-7</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4041,13 +4045,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>42076.74</v>
+        <v>5193.3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1658-2410-CM26</t>
+          <t>1057417-15339-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4072,47 +4076,43 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TRANSPORTES ALV-BAACK SPA</t>
+          <t>TURISMO AYEKANTUN LIMITADA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>77.314.274-2</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.470.279-4</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>41604.95</v>
+        <v>42076.74</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2291-1412-CM26</t>
+          <t>1658-2410-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4137,43 +4137,47 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>69.190.700-7</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rentur Chile SpA </t>
+          <t>TRANSPORTES ALV-BAACK SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>76.241.697-2</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
+          <t>77.314.274-2</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>5705.32</v>
+        <v>41604.95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2291-1414-CM26</t>
+          <t>2291-1412-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4193,7 +4197,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4213,32 +4217,28 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MARPACIFICO SPA</t>
+          <t xml:space="preserve">Rentur Chile SpA </t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>77.173.533-9</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
+          <t>76.241.697-2</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6978.05</v>
+        <v>5705.32</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1057499-444-CM26</t>
+          <t>2291-1414-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4253,42 +4253,42 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.608.108-K</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
+          <t>MARPACIFICO SPA</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.791.832-1</t>
+          <t>77.173.533-9</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4297,7 +4297,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>9472.790000000001</v>
+        <v>6978.05</v>
       </c>
     </row>
     <row r="63">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4555,7 +4555,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1057499-445-CM26</t>
+          <t>1057499-444-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4614,13 +4614,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>9554.450000000001</v>
+        <v>9472.790000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>3474-488-CM26</t>
+          <t>1057499-445-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4645,12 +4645,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.608.108-K</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE SALUD SUR UNIDAD HOSPITALARI</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>YANGUAS TRANSPORTE TURISTICO</t>
+          <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>78.973.230-2</t>
+          <t>76.791.832-1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -4679,13 +4679,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>33034.99</v>
+        <v>9554.450000000001</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>4650-122-CM26</t>
+          <t>3474-488-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4725,28 +4725,32 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Marcelo Fabian</t>
+          <t>YANGUAS TRANSPORTE TURISTICO</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.621.909-8</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
+          <t>78.973.230-2</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>272.21</v>
+        <v>33034.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>932-152-CM26</t>
+          <t>4650-122-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4766,32 +4770,32 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
+          <t>Marcelo Fabian</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.036.979-9</t>
+          <t>76.621.909-8</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4801,13 +4805,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>17149.02</v>
+        <v>272.21</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1443565-45-CM26</t>
+          <t>932-152-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4822,37 +4826,37 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.312.000-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>INIA</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>arriendo</t>
+          <t>Sociedad de Transporte Jiménez Hermanos Ltda.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>99.501.690-7</t>
+          <t>76.036.979-9</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4862,13 +4866,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>408.91</v>
+        <v>17149.02</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>932-155-CM26</t>
+          <t>1443565-45-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4893,27 +4897,27 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.312.000-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>INIA</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>CAR PLACE SPA</t>
+          <t>arriendo</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.704.974-9</t>
+          <t>99.501.690-7</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4923,13 +4927,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>35882.19</v>
+        <v>408.91</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1305532-73-CM26</t>
+          <t>932-155-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4944,7 +4948,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4954,27 +4958,27 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.981.040-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>VIVANET</t>
+          <t>CAR PLACE SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.018.259-1</t>
+          <t>76.704.974-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4984,13 +4988,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>12914.61</v>
+        <v>35882.19</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1197-107-CM26</t>
+          <t>1305532-73-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5015,27 +5019,27 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.981.040-6</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL ELQUI</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Felipe </t>
+          <t>VIVANET</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.834.013-7</t>
+          <t>76.018.259-1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
@@ -5045,71 +5049,132 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1452.68</v>
+        <v>12914.61</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>1197-107-CM26</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>61.107.000-4</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Felipe </t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>76.834.013-7</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>1452.68</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
           <t>2793-854-CM26</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>2239-12-LR25</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>ago-2026</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2239-12-LR25</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="E76" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>69.255.400-0</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>TERESA GARRIDO ROJAS E HIJOS LTDA</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>76.791.832-1</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="n">
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="n">
         <v>36806.65</v>
       </c>
     </row>
